--- a/sampleprojects/CorporateTax/excel/states/KY_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/KY_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts or 200 transactions); result.ky_gross_receipts is greater than or equal to result.ky_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.ky_gross_receipts &gt;= result.ky_economic_nexus_threshold</t>
+    <t>ky_result.gross_receipts &gt;= ky_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.ky_has_nexus = true;</t>
+    <t>set ky_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.ky_has_nexus = false; set result.ky_tax_liability = 0.0;</t>
+    <t>set ky_result.has_nexus = false; set ky_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate KY Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Kentucky nexus</t>
   </si>
   <si>
-    <t>result.ky_has_nexus is equal to true</t>
+    <t>ky_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Kentucky state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.ky_state_additions = 0.0; if result.ky_us_interest_income != 0.0 then set result.ky_state_additions = result.ky_state_additions + result.ky_us_interest_income; endif set result.ky_state_subtractions = 0.0; if result.ky_municipal_interest != 0.0 then set result.ky_state_subtractions = result.ky_state_subtractions + result.ky_municipal_interest; endif if result.ky_dividends_from_ky_corps != 0.0 then set result.ky_state_subtractions = result.ky_state_subtractions + result.ky_dividends_from_ky_corps; endif add (("Kentucky additions: $" + string value of (result.ky_state_additions)) + ", subtractions: $") + string value of (result.ky_state_subtractions) to job.audit_trail;</t>
+    <t>set ky_result.state_additions = 0.0; if ky_result.us_interest_income != 0.0 then set ky_result.state_additions = ky_result.state_additions + ky_result.us_interest_income; endif set ky_result.state_subtractions = 0.0; if ky_result.municipal_interest != 0.0 then set ky_result.state_subtractions = ky_result.state_subtractions + ky_result.municipal_interest; endif if ky_result.dividends_from_ky_corps != 0.0 then set ky_result.state_subtractions = ky_result.state_subtractions + ky_result.dividends_from_ky_corps; endif add (("Kentucky additions: $" + string value of (ky_result.state_additions)) + ", subtractions: $") + string value of (ky_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.ky_state_additions = 0.0; set result.ky_state_subtractions = 0.0;</t>
+    <t>set ky_result.state_additions = 0.0; set ky_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate KY State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.ky_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.ky_apportioned_income &gt; 0.0</t>
+    <t>ky_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Kentucky corporate tax (flat rate 4.5%); Apply Kentucky 4.5% flat rate</t>
   </si>
   <si>
-    <t>set result.ky_taxable_income = the maximum of (result.ky_apportioned_income + result.ky_state_additions - result.ky_state_subtractions) and (0.0); set result.ky_tax_liability = the maximum of (result.ky_taxable_income * result.ky_corp_tax_rate - result.ky_state_credits) and (0.0); set result.ky_refund_or_owed = result.ky_estimated_payments - result.ky_tax_liability; add "Kentucky taxable income: $" + string value of (result.ky_taxable_income) to job.audit_trail; add "Kentucky tax liability (4.5%): $" + string value of (result.ky_tax_liability) to job.audit_trail;</t>
+    <t>set ky_result.taxable_income = the maximum of (ky_result.apportioned_income + ky_result.state_additions - ky_result.state_subtractions) and (0.0); set ky_result.tax_liability = the maximum of (ky_result.taxable_income * ky_result.corp_tax_rate - ky_result.state_credits) and (0.0); set ky_result.refund_or_owed = ky_result.estimated_payments - ky_result.tax_liability; add "Kentucky taxable income: $" + string value of (ky_result.taxable_income) to job.audit_trail; add "Kentucky tax liability (4.5%): $" + string value of (ky_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.ky_taxable_income = 0.0; set result.ky_tax_liability = 0.0;</t>
+    <t>set ky_result.taxable_income = 0.0; set ky_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,13 +205,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>ky_result</t>
   </si>
   <si>
     <t>(17 attributes)</t>
   </si>
   <si>
-    <t>ky_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -226,7 +226,7 @@
     <t>Declared from decision-table usage; referenced by KY but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>ky_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -238,7 +238,7 @@
     <t>KY uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>ky_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.045</t>
@@ -247,10 +247,10 @@
     <t>KY corporate income tax rate: 4.5% flat rate (KRS 141.040, effective 2025)</t>
   </si>
   <si>
-    <t>ky_dividends_from_ky_corps</t>
-  </si>
-  <si>
-    <t>ky_economic_nexus_threshold</t>
+    <t>dividends_from_ky_corps</t>
+  </si>
+  <si>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -259,13 +259,13 @@
     <t>KY economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>ky_estimated_payments</t>
-  </si>
-  <si>
-    <t>ky_gross_receipts</t>
-  </si>
-  <si>
-    <t>ky_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -277,43 +277,43 @@
     <t>Whether corporation has nexus with Kentucky</t>
   </si>
   <si>
-    <t>ky_municipal_interest</t>
-  </si>
-  <si>
-    <t>ky_refund_or_owed</t>
-  </si>
-  <si>
-    <t>ky_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>KY additions to federal taxable income (federal interest income, IRC 199A addback, state tax refunds, etc.)</t>
   </si>
   <si>
-    <t>ky_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>KY tax credits (industrial development, film industry, coal incentive, recycling, etc.)</t>
   </si>
   <si>
-    <t>ky_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>KY subtractions from federal taxable income (KY municipal bond interest, dividends from KY corporations, etc.)</t>
   </si>
   <si>
-    <t>ky_tax_liability</t>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>KY corporate income tax liability</t>
   </si>
   <si>
-    <t>ky_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>KY taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>ky_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -325,7 +325,7 @@
     <t>KY economic nexus transaction count threshold: 200 transactions</t>
   </si>
   <si>
-    <t>ky_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
